--- a/reports/jobs_2026-10-20.xlsx
+++ b/reports/jobs_2026-10-20.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$109</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I105"/>
+  <dimension ref="A1:I109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -520,17 +520,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Arm India</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Principle Machine Learning Engineer</t>
+          <t>Application Engineer - Chip Methodology and Automation</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -538,7 +538,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -546,12 +550,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27455</t>
+          <t>https://careers.arm.com/job/bengaluru/application-engineer-chip-methodology-and-automation/33099/102190194384</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://careers.arm.com/</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -563,17 +567,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Arm India</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Physical Design Engineer</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -583,7 +587,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -593,12 +597,12 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25538</t>
+          <t>https://careers.arm.com/job/bengaluru/physical-design-engineer/33099/102190154656</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://careers.arm.com/</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -608,61 +612,57 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Paytm</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Talent Acquisition Intern - IT Recruitment</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Noida, Uttar Pradesh</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/paytm/95eadc2b-27bf-40fe-b6e6-93aaeadd08f7</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/paytm</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Agnikul Cosmos</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Careers Inquiries humancapital@agnikul.in</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>mailto:%20humancapital@agnikul.in</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>https://agnikul.in/careers</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Agnikul Cosmos</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Careers Inquiries humancapital@agnikul.in</t>
+          <t>Chiang Mai 0 available jobs</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -675,7 +675,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai 0 available jobs Ok</t>
+        </is>
+      </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -683,12 +687,12 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>mailto:%20humancapital@agnikul.in</t>
+          <t>https://careersatagoda.com/location/chiang-mai/</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>https://agnikul.in/careers</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -705,7 +709,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Chiang Mai 0 available jobs</t>
+          <t>Dubai 0 available jobs</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -730,7 +734,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/chiang-mai/</t>
+          <t>https://careersatagoda.com/location/dubai/</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -752,7 +756,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Dubai 0 available jobs</t>
+          <t>Mumbai 0 available jobs</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -777,7 +781,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/dubai/</t>
+          <t>https://careersatagoda.com/location/mumbai/</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -799,7 +803,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Mumbai 0 available jobs</t>
+          <t>Shanghai 2 available jobs</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -824,7 +828,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/mumbai/</t>
+          <t>https://careersatagoda.com/location/shanghai/</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -846,7 +850,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Shanghai 2 available jobs</t>
+          <t>Engineering &amp; Technology</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -859,11 +863,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai 0 available jobs Ok</t>
-        </is>
-      </c>
+      <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -871,7 +871,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/shanghai/</t>
+          <t>https://careersatagoda.com/department/technology/</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Engineering &amp; Technology</t>
+          <t>Key Takeaways from Agoda’s AI Developer Report 2026 September 29, 2026 /</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/department/technology/</t>
+          <t>https://careersatagoda.com/blog/tech/key-takeaways-from-agodas-ai-developer-report-2026/</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Key Takeaways from Agoda’s AI Developer Report 2026 September 29, 2026 /</t>
+          <t>How Agoda is evolving engineering support with AI agents September 22, 2026 /</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/blog/tech/key-takeaways-from-agodas-ai-developer-report-2026/</t>
+          <t>https://careersatagoda.com/blog/tech/how-agoda-is-evolving-engineering-support-with-ai-agents/</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>How Agoda is evolving engineering support with AI agents September 22, 2026 /</t>
+          <t>Mumbai jobs</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -992,7 +992,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai jobs Yokohama jobs</t>
+        </is>
+      </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -1000,7 +1004,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/blog/tech/how-agoda-is-evolving-engineering-support-with-ai-agents/</t>
+          <t>https://careersatagoda.com/location/mumbai-india/</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1022,12 +1026,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Mumbai jobs</t>
+          <t>Backend Developer Jobs</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1035,11 +1039,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai jobs Yokohama jobs</t>
-        </is>
-      </c>
+      <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/mumbai-india/</t>
+          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer Jobs</t>
+          <t>Full Stack Developer Jobs</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
+          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Developer Jobs</t>
+          <t>Software Engineer Jobs</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
+          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1150,12 +1150,12 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Agoda India</t>
+          <t>Arm India</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Jobs</t>
+          <t>Theorem Proving Engineer</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
+          <t>https://careers.arm.com/job/austin/theorem-proving-engineer/33099/97584421536</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/</t>
+          <t>https://careers.arm.com/</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25539</t>
+          <t>https://www.atlassian.com/company/careers/details/25538</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack (Loom Billing &amp; Integrations)</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27431</t>
+          <t>https://www.atlassian.com/company/careers/details/25539</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Principle Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1395,11 +1395,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -1407,7 +1403,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25561</t>
+          <t>https://www.atlassian.com/company/careers/details/27455</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1429,12 +1425,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer – Full Stack (Loom Billing &amp; Integrations)</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1442,7 +1438,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26758</t>
+          <t>https://www.atlassian.com/company/careers/details/27431</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1472,12 +1472,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning System Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27388</t>
+          <t>https://www.atlassian.com/company/careers/details/25561</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>EMEA Field CTO, DX — Engineering Executive Advisor</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1532,11 +1532,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E24" s="4" t="inlineStr"/>
       <c r="F24" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -1544,7 +1540,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/24899</t>
+          <t>https://www.atlassian.com/company/careers/details/26758</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1566,12 +1562,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Data Engineer, 2027 Graduate U.S</t>
+          <t>Machine Learning System Engineer</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1579,7 +1575,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25998</t>
+          <t>https://www.atlassian.com/company/careers/details/27388</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, 2027 Graduate U.S.</t>
+          <t>EMEA Field CTO, DX — Engineering Executive Advisor</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1622,7 +1622,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -1630,7 +1634,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25813</t>
+          <t>https://www.atlassian.com/company/careers/details/24899</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -1652,12 +1656,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, 2027 Graduate U.S.</t>
+          <t>Data Engineer, 2027 Graduate U.S</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1673,7 +1677,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25999</t>
+          <t>https://www.atlassian.com/company/careers/details/25998</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -1695,7 +1699,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, 2027 Graduate Canada</t>
+          <t>Software Engineer, 2027 Graduate U.S.</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1716,7 +1720,7 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26070</t>
+          <t>https://www.atlassian.com/company/careers/details/25813</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -1738,12 +1742,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Product Design Intern, 2027 Summer U.S.</t>
+          <t>Machine Learning Engineer, 2027 Graduate U.S.</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1751,11 +1755,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E29" s="4" t="inlineStr"/>
       <c r="F29" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26273</t>
+          <t>https://www.atlassian.com/company/careers/details/25999</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -1785,12 +1785,12 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Data Engineer Intern, 2027 Summer U.S.</t>
+          <t>Software Engineer, 2027 Graduate Canada</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1798,11 +1798,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E30" s="4" t="inlineStr"/>
       <c r="F30" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -1810,7 +1806,7 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26272</t>
+          <t>https://www.atlassian.com/company/careers/details/26070</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -1832,7 +1828,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Product Management Intern, 2027 Summer U.S.</t>
+          <t>Product Design Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1857,7 +1853,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26274</t>
+          <t>https://www.atlassian.com/company/careers/details/26273</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -1879,12 +1875,12 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Intern, 2027 Summer U.S.</t>
+          <t>Data Engineer Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1892,7 +1888,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr"/>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26268</t>
+          <t>https://www.atlassian.com/company/careers/details/26272</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Research Intern, 2027 Summer U.S.</t>
+          <t>Product Management Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1935,7 +1935,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -1943,7 +1947,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26270</t>
+          <t>https://www.atlassian.com/company/careers/details/26274</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -1965,12 +1969,12 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Security Engineer Intern, 2027 Summer U.S.</t>
+          <t>Machine Learning Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -1986,7 +1990,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26267</t>
+          <t>https://www.atlassian.com/company/careers/details/26268</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2008,7 +2012,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, 2027 Canada</t>
+          <t>Research Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2029,7 +2033,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26275</t>
+          <t>https://www.atlassian.com/company/careers/details/26270</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2051,7 +2055,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>AI Demand Intelligence Intern, 2027 Summer U.S.</t>
+          <t>Security Engineer Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2064,11 +2068,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E36" s="4" t="inlineStr"/>
       <c r="F36" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26843</t>
+          <t>https://www.atlassian.com/company/careers/details/26267</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, 2027 Summer U.S.</t>
+          <t>Software Engineer Intern, 2027 Canada</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26266</t>
+          <t>https://www.atlassian.com/company/careers/details/26275</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2141,12 +2141,12 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Enterprise Security Engineer</t>
+          <t>AI Demand Intelligence Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27275</t>
+          <t>https://www.atlassian.com/company/careers/details/26843</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Enterprise Security Engineer</t>
+          <t>Software Engineer Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2201,11 +2201,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -2213,7 +2209,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26986</t>
+          <t>https://www.atlassian.com/company/careers/details/26266</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -2235,12 +2231,12 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Security Testing Engineer - Penetration Tester</t>
+          <t>Enterprise Security Engineer</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2250,7 +2246,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Remote or Remote</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -2260,7 +2256,7 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26643</t>
+          <t>https://www.atlassian.com/company/careers/details/27275</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -2277,12 +2273,12 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Chargebee</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Product Launch and price new features without waiting on engineering</t>
+          <t>Enterprise Security Engineer</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2295,7 +2291,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr"/>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -2303,12 +2303,12 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/solutions/role/product/</t>
+          <t>https://www.atlassian.com/company/careers/details/26986</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/careers/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
@@ -2320,17 +2320,17 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Chargebee</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Growth Test offers, run promotions and lift conversion</t>
+          <t>Security Testing Engineer - Penetration Tester</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2338,7 +2338,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr"/>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Remote or Remote</t>
+        </is>
+      </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -2346,12 +2350,12 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/solutions/role/growth/</t>
+          <t>https://www.atlassian.com/company/careers/details/26643</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/careers/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
@@ -2363,12 +2367,12 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Chargebee</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Implementation Engineer 2</t>
+          <t>Product Launch and price new features without waiting on engineering</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2381,11 +2385,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -2393,12 +2393,12 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
+          <t>https://www.chargebee.com/solutions/role/product/</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://www.chargebee.com/careers/</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
@@ -2410,17 +2410,17 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Chargebee</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
+          <t>Growth Test offers, run promotions and lift conversion</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2428,11 +2428,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>India Full-time</t>
-        </is>
-      </c>
+      <c r="E44" s="4" t="inlineStr"/>
       <c r="F44" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -2440,12 +2436,12 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
+          <t>https://www.chargebee.com/solutions/role/growth/</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://www.chargebee.com/careers/</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -2462,7 +2458,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer-3</t>
+          <t>Implementation Engineer 2</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -2487,7 +2483,7 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-707788-integration--customisation-engineer3</t>
+          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -2509,12 +2505,12 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customization Engineer -1</t>
+          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2534,7 +2530,7 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
+          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -2556,12 +2552,12 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
+          <t>Integration &amp; Customisation Engineer-3</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2569,7 +2565,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr"/>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
+          <t>https://exotel.com/about-us/careers/#op-707788-integration--customisation-engineer3</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Billing)</t>
+          <t>Integration &amp; Customization Engineer -1</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>India Full-time</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-700106-software-engineer-2-billing</t>
+          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 3 (Voice)</t>
+          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -2659,11 +2659,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E49" s="4" t="inlineStr"/>
       <c r="F49" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -2671,7 +2667,7 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704555-software-engineer-3-voice</t>
+          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -2693,7 +2689,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 2</t>
+          <t>Software Engineer - 2 (Billing)</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -2718,7 +2714,7 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
+          <t>https://exotel.com/about-us/careers/#op-700106-software-engineer-2-billing</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -2740,7 +2736,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 3</t>
+          <t>Software Engineer - 3 (Voice)</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -2765,7 +2761,7 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
+          <t>https://exotel.com/about-us/careers/#op-704555-software-engineer-3-voice</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -2787,7 +2783,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Product Head, Voice AI</t>
+          <t>Forward Deployed Engineer - 2</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -2812,7 +2808,7 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
+          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -2834,12 +2830,12 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Software Developer - 3 (Voice4Ai-Backend)</t>
+          <t>Forward Deployed Engineer - 3</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -2859,7 +2855,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-voice4aibackend</t>
+          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -2881,7 +2877,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Voicebot)</t>
+          <t>Product Head, Voice AI</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -2906,7 +2902,7 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
+          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -2928,7 +2924,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
+          <t>Software Developer - 3 (Voice4Ai-Backend)</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -2953,7 +2949,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
+          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-voice4aibackend</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -2970,17 +2966,17 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS</t>
+          <t>Software Engineer - 2 (Voicebot)</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -2988,7 +2984,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr"/>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -2996,12 +2996,12 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Data-Engineer---AWS_SR-37522</t>
+          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
@@ -3013,17 +3013,17 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>GenAI-Engineer</t>
+          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -3031,7 +3031,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr"/>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -3039,12 +3043,12 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/GenAI-Engineer_SR-46807</t>
+          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
@@ -3061,12 +3065,12 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engineer - AWS</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -3082,7 +3086,7 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/New-Jersey/AI-Engineer_SR-46455-1</t>
+          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Data-Engineer---AWS_SR-37522</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -3104,7 +3108,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>GenAI-Engineer</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -3125,7 +3129,7 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/New-York/MLOps-Engineer_SR-46499-1</t>
+          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/GenAI-Engineer_SR-46807</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -3142,17 +3146,17 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>GitLab India</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Software composition analysis</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -3168,12 +3172,12 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/solutions/supply-chain/</t>
+          <t>https://fractal.ai/en-US/Careers/job/New-Jersey/AI-Engineer_SR-46455-1</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/jobs/all-jobs/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -3185,17 +3189,17 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Internships and Programs</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -3211,12 +3215,12 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
+          <t>https://fractal.ai/en-US/Careers/job/New-York/MLOps-Engineer_SR-46499-1</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
@@ -3228,12 +3232,12 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>GitLab India</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
+          <t>Software composition analysis</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -3254,12 +3258,12 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
+          <t>https://about.gitlab.com/solutions/supply-chain/</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://about.gitlab.com/jobs/all-jobs/</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
@@ -3271,12 +3275,12 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Internships and Programs</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -3289,11 +3293,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru-VTP, India</t>
-        </is>
-      </c>
+      <c r="E63" s="4" t="inlineStr"/>
       <c r="F63" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -3301,12 +3301,12 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
@@ -3318,12 +3318,12 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>HighRadius</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -3336,11 +3336,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>Hyderabad, Telangana, India</t>
-        </is>
-      </c>
+      <c r="E64" s="4" t="inlineStr"/>
       <c r="F64" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -3348,12 +3344,12 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
+          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/highradius</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
@@ -3365,17 +3361,17 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -3385,7 +3381,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>New Delhi, in</t>
+          <t>Bengaluru-VTP, India</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -3395,12 +3391,12 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -3412,17 +3408,17 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>HighRadius</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -3432,7 +3428,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -3442,12 +3438,12 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
+          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/lendingkart</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -3459,17 +3455,17 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Internship Opportunities</t>
+          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -3477,7 +3473,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr"/>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>New Delhi, in</t>
+        </is>
+      </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -3485,12 +3485,12 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/pathways-programs/internships</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
@@ -3502,17 +3502,17 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -3520,7 +3520,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr"/>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -3528,12 +3532,12 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/Teams/Engineering</t>
+          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
@@ -3545,17 +3549,17 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Cluster Head- Last mile - Chennai</t>
+          <t>Internship Opportunities</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -3563,11 +3567,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>Chennai, Tamil Nadu</t>
-        </is>
-      </c>
+      <c r="E69" s="4" t="inlineStr"/>
       <c r="F69" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
+          <t>https://careers.linkedin.com/pathways-programs/internships</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
@@ -3592,12 +3592,12 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Trainee - Recruitment Coordinator</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -3610,11 +3610,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+      <c r="E70" s="4" t="inlineStr"/>
       <c r="F70" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -3622,12 +3618,12 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
+          <t>https://careers.linkedin.com/Teams/Engineering</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
@@ -3639,12 +3635,12 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>MongoDB India</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Engineer 3 - Business Systems</t>
+          <t>Cluster Head- Last mile - Chennai</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -3659,7 +3655,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Chennai, Tamil Nadu</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -3669,12 +3665,12 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
+          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/mongodb</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
@@ -3686,17 +3682,17 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>TESTING</t>
+          <t>Trainee - Recruitment Coordinator</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -3704,7 +3700,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr"/>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
+          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
@@ -3729,12 +3729,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Open Financial</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Careers Hiring across engineering, design, product, GTM &amp; ops.</t>
+          <t>For Developers</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -3747,11 +3747,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>India’s 100 th unicorn. C</t>
-        </is>
-      </c>
+      <c r="E73" s="4" t="inlineStr"/>
       <c r="F73" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -3759,12 +3755,12 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>https://open.money/company/careers.html</t>
+          <t>https://www.moengage.com/role/for-developers/</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>https://open.money/careers</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
@@ -3776,17 +3772,17 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>PTC India</t>
+          <t>MongoDB India</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Learn more about PTC internships</t>
+          <t>Engineer 3 - Business Systems</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -3794,7 +3790,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr"/>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -3802,12 +3802,12 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers/internships</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
@@ -3819,17 +3819,17 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Intern - Talent Acquisition</t>
+          <t>TESTING</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -3837,11 +3837,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, Haryana</t>
-        </is>
-      </c>
+      <c r="E75" s="4" t="inlineStr"/>
       <c r="F75" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -3849,12 +3845,12 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/426a6834-1397-4e65-94af-69874c790805</t>
+          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://careers.mphasis.com/</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -3866,17 +3862,17 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Open Financial</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Intern-Talent Acquisition</t>
+          <t>Careers Hiring across engineering, design, product, GTM &amp; ops.</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -3886,7 +3882,7 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India’s 100 th unicorn. C</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -3896,12 +3892,12 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
+          <t>https://open.money/company/careers.html</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://open.money/careers</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
@@ -3913,12 +3909,12 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>PTC India</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Internship - Talent Acquisition</t>
+          <t>Learn more about PTC internships</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -3931,11 +3927,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>Noida, Uttar Pradesh</t>
-        </is>
-      </c>
+      <c r="E77" s="4" t="inlineStr"/>
       <c r="F77" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -3943,12 +3935,12 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
+          <t>https://www.ptc.com/en/careers/internships</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://www.ptc.com/en/careers</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
@@ -3965,7 +3957,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern</t>
+          <t>Intern - Talent Acquisition</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -3980,7 +3972,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Gurugram, Haryana</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -3990,7 +3982,7 @@
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/6d7551f7-34c3-46a2-a4e4-18b29f15338c</t>
+          <t>https://jobs.lever.co/paytm/426a6834-1397-4e65-94af-69874c790805</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -4012,7 +4004,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Bangalore</t>
+          <t>Intern-Talent Acquisition</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -4037,7 +4029,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
+          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -4059,7 +4051,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition- Intern || Noida ||</t>
+          <t>Internship - Talent Acquisition</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -4084,7 +4076,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/648841ab-2778-4759-a4c9-eabae97ec65d</t>
+          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -4101,17 +4093,17 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Publicis Sapient India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Join our engineering talent community</t>
+          <t>Talent Acquisition Intern</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -4119,7 +4111,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr"/>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>Noida, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -4127,12 +4123,12 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
+          <t>https://jobs.lever.co/paytm/6d7551f7-34c3-46a2-a4e4-18b29f15338c</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>https://careers.publicissapient.com/</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
@@ -4144,17 +4140,17 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Talent Acquisition Intern - Bangalore</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -4164,7 +4160,7 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -4174,12 +4170,12 @@
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
+          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
@@ -4191,17 +4187,17 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>Talent Acquisition Intern - IT Recruitment</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -4211,7 +4207,7 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -4221,12 +4217,12 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
+          <t>https://jobs.lever.co/paytm/95eadc2b-27bf-40fe-b6e6-93aaeadd08f7</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
@@ -4238,17 +4234,17 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Node.js Developer</t>
+          <t>Talent Acquisition- Intern || Noida ||</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -4258,7 +4254,7 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -4268,12 +4264,12 @@
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
+          <t>https://jobs.lever.co/paytm/648841ab-2778-4759-a4c9-eabae97ec65d</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
@@ -4285,17 +4281,17 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Ramco Systems</t>
+          <t>Publicis Sapient India</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Internships</t>
+          <t>Join our engineering talent community</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -4311,12 +4307,12 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
+          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/</t>
+          <t>https://careers.publicissapient.com/</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
@@ -4328,17 +4324,17 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>ENG Project/ Program - Intern</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -4348,7 +4344,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -4358,12 +4354,12 @@
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I86" s="4" t="inlineStr">
@@ -4375,12 +4371,12 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Industrial Trainee</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -4395,7 +4391,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -4405,12 +4401,12 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8266405?gh_jid=8266405</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
@@ -4422,17 +4418,17 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security Engineer - Identity and Access </t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -4442,7 +4438,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, India</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -4452,12 +4448,12 @@
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr">
@@ -4469,29 +4465,25 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Ramco Systems</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud: Azure</t>
+          <t>Internships</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>0-2 years</t>
-        </is>
-      </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bangalore </t>
-        </is>
-      </c>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr"/>
       <c r="F89" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -4499,12 +4491,12 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8258200?gh_jid=8258200</t>
+          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://www.ramco.com/careers/</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
@@ -4521,12 +4513,12 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - IAM</t>
+          <t>ENG Project/ Program - Intern</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -4536,7 +4528,7 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
@@ -4546,7 +4538,7 @@
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -4568,7 +4560,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer- SaaS O365</t>
+          <t>Industrial Trainee</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -4578,12 +4570,12 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>0-2 years</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bangalore </t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -4593,7 +4585,7 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8256407?gh_jid=8256407</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8266405?gh_jid=8266405</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -4610,17 +4602,17 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>Scaler</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
+          <t xml:space="preserve">Security Engineer - Identity and Access </t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -4630,7 +4622,7 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Remote Instructor- Python</t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
@@ -4640,12 +4632,12 @@
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/remote-instructor-python</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
@@ -4657,25 +4649,29 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
+          <t>Software Engineer - Cloud: Azure</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="inlineStr"/>
+          <t>0-2 years</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bangalore </t>
+        </is>
+      </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -4683,12 +4679,12 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzgsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8258200?gh_jid=8258200</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
@@ -4700,12 +4696,12 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>AI Screenplay Writer</t>
+          <t>Software Engineer - IAM</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -4718,7 +4714,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr"/>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzMsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
@@ -4743,12 +4743,12 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>AI Video Editor</t>
+          <t>Software Engineer- SaaS O365</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -4758,10 +4758,14 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr"/>
+          <t>0-2 years</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bangalore </t>
+        </is>
+      </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -4769,12 +4773,12 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTIsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8256407?gh_jid=8256407</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
@@ -4786,17 +4790,17 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Scaler</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>AI Sound Designer</t>
+          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -4804,7 +4808,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr"/>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>Remote Instructor- Python</t>
+        </is>
+      </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -4812,12 +4820,12 @@
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.scaler.com/careers/remote-instructor-python</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://www.scaler.com/careers/</t>
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr">
@@ -4834,12 +4842,12 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>AI Animator</t>
+          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -4855,7 +4863,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzgsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -4872,17 +4880,17 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>AI Screenplay Writer</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -4890,11 +4898,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E98" s="4" t="inlineStr"/>
       <c r="F98" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -4902,12 +4906,12 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzMsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr">
@@ -4919,17 +4923,17 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+          <t>AI Video Editor</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -4937,11 +4941,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E99" s="4" t="inlineStr"/>
       <c r="F99" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -4949,12 +4949,12 @@
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTIsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
@@ -4966,17 +4966,17 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>SirionLabs</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Intern- Employee Engagement</t>
+          <t>AI Sound Designer</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>https://www.sirion.ai/jobs/intern-employee-engagement/</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>https://www.sirionlabs.com/careers/</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I100" s="4" t="inlineStr">
@@ -5009,17 +5009,17 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>Sprinklr</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Internship and Early Careers</t>
+          <t>AI Animator</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -5035,12 +5035,12 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
@@ -5052,17 +5052,17 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>Stripe India</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Gurugram, in</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/stripe</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I102" s="4" t="inlineStr">
@@ -5099,17 +5099,17 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>Thoughtworks India</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Software Procurement Intern</t>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Gurgaon, India; Pune, India</t>
+          <t>Gurugram, in</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>https://www.thoughtworks.com/careers/jobs/8236673?gh_jid=8236673</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/thoughtworks</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
@@ -5146,17 +5146,17 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>Unacademy</t>
+          <t>SirionLabs</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Test Jerin</t>
+          <t>Intern- Employee Engagement</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -5164,11 +5164,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E104" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
+      <c r="E104" s="4" t="inlineStr"/>
       <c r="F104" s="4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -5176,12 +5172,12 @@
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+          <t>https://www.sirion.ai/jobs/intern-employee-engagement/</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
+          <t>https://www.sirionlabs.com/careers/</t>
         </is>
       </c>
       <c r="I104" s="4" t="inlineStr">
@@ -5193,52 +5189,236 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
+          <t>Sprinklr</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>Internship and Early Careers</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr"/>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
+        </is>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sprinklr.com/careers/</t>
+        </is>
+      </c>
+      <c r="I105" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>Stripe India</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer, Intern</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/stripe</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>Thoughtworks India</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>Software Procurement Intern</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>Gurgaon, India; Pune, India</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>https://www.thoughtworks.com/careers/jobs/8236673?gh_jid=8236673</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/thoughtworks</t>
+        </is>
+      </c>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
           <t>Unacademy</t>
         </is>
       </c>
-      <c r="B105" s="4" t="inlineStr">
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>Test Jerin</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
+        </is>
+      </c>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>Unacademy</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
         <is>
           <t>Software Engineer, Backend</t>
         </is>
       </c>
-      <c r="C105" s="4" t="inlineStr">
+      <c r="C109" s="4" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="D105" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E105" s="4" t="inlineStr">
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
         <is>
           <t>Bengaluru, in</t>
         </is>
       </c>
-      <c r="F105" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="G105" s="5" t="inlineStr">
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
         <is>
           <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
         </is>
       </c>
-      <c r="H105" s="4" t="inlineStr">
+      <c r="H109" s="4" t="inlineStr">
         <is>
           <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
-      <c r="I105" s="4" t="inlineStr">
+      <c r="I109" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I105"/>
+  <autoFilter ref="A1:I109"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -5344,6 +5524,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId108"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5355,7 +5539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5383,35 +5567,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INDmoney</t>
+          <t>Cuemath</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.indmoney.com/careers</t>
+          <t>https://www.cuemath.com/careers/</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.indmoney.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Cuemath</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://www.cuemath.com/careers/</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5420,18 +5584,18 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Log9 Materials</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>https://www.log9materials.com/careers</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5440,18 +5604,18 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Signzy</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>https://www.signzy.com/careers/</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5460,18 +5624,18 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Ather Energy</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>https://www.atherenergy.com/careers</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5480,18 +5644,18 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Blinkit</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>https://blinkit.com/careers</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5500,18 +5664,18 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Capillary Technologies</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>https://www.capillarytech.com/careers/</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5520,18 +5684,18 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>CRED</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>https://careers.cred.club/</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5540,18 +5704,18 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Cleartrip</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>https://www.cleartrip.com/careers</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5560,18 +5724,18 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Nykaa</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>https://www.nykaa.com/careers</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
 Call log:
@@ -5580,18 +5744,18 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Juspay</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://juspay.io/careers</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5600,18 +5764,18 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>MakeMyTrip</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>https://careers.makemytrip.com/</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5620,58 +5784,18 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>FarEye</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>https://fareye.com/careers</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://fareye.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>FirstCry</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>https://www.firstcry.com/careers</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.firstcry.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>OYO</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://www.oyorooms.com/careers/</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5680,38 +5804,18 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Tredence</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>https://www.tredence.com/careers</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: net::ERR_CONNECTION_RESET at https://www.tredence.com/careers
-Call log:
-  - navigating to "https://www.tredence.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Zomato</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>https://www.zomato.com/careers</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.zomato.com/careers
 Call log:
@@ -5720,38 +5824,18 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Shiprocket</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>https://www.shiprocket.in/careers/</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.shiprocket.in/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Swiggy</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>https://careers.swiggy.com/</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5760,18 +5844,18 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Coforge</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>https://www.coforge.com/careers</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -5780,18 +5864,18 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -5800,18 +5884,18 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Udaan</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>https://udaan.com/careers</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
